--- a/docs/AI-Usage/AI Usage Register/AI Usage Register v0.3.xlsx
+++ b/docs/AI-Usage/AI Usage Register/AI Usage Register v0.3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cjbur\Desktop\New folder (2)\Ticketing-System\docs\AI-Usage\AI Usage Register\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c906530d9ff38bc/Desktop/SEN381/Ticketing-System/docs/AI-Usage/AI Usage Register/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E7AE79-4618-4BF0-9238-AF7795BE5308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{60E7AE79-4618-4BF0-9238-AF7795BE5308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78636C9E-7F60-4274-B590-C77D893ECCDC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5AB626C0-9419-4ED9-8516-202D1A580094}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{5AB626C0-9419-4ED9-8516-202D1A580094}"/>
   </bookViews>
   <sheets>
     <sheet name="AI Usage Register" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -251,21 +251,12 @@
     <t>Drafted 13 candidate project-specific risks derived from the Master Brief s.2 failures and the team's scope, constraint and decision artefacts, each with cause, early-warning indicator, preventive mitigation and contingency. Drafted the probability and impact scale definitions and the 1–2 / 3–4 / 6–9 priority bands.</t>
   </si>
   <si>
-    <t>[YOU MUST COMPLETE — see guidance]</t>
-  </si>
-  <si>
     <t>Forward Engineering Considerations register</t>
   </si>
   <si>
     <t>Drafted 7 forward concerns (security and personal information, migration and cut-over, testability, technology availability, deployment platform, observability, operational cost), each recording why it matters now, the later decision influenced, information still missing and the risk of ignoring it. Drafted the influence mapping showing what each changed in the M1 baseline.</t>
   </si>
   <si>
-    <t>Member C working pack — ownership, sequencing, GitHub spec</t>
-  </si>
-  <si>
-    <t>Drafted the artefact ownership map, the dependency sequence between Members A, B and C, the Phase 1 repository specification, the PED s.1.4 clause mapping and a review checklist.</t>
-  </si>
-  <si>
     <t>08 Sept 2026</t>
   </si>
   <si>
@@ -326,9 +317,6 @@
     <t>Populated the 'Linked FR / NFR / RSK' column, which cited no FR or NFR at all, with mappings to Member B's requirements; recorded FEC-002 as having no requirement coverage, with the reason, rather than leaving it blank. Named the owner, differentiated the status values, and updated the influence-sheet asks against what A and B had actually delivered.</t>
   </si>
   <si>
-    <t>[YOU MUST COMPLETE — see guidance] — check the FR/NFR mappings yourself, especially FEC-001 and FEC-006, since those are the rows you cite in PED s.9.2 and will defend orally.</t>
-  </si>
-  <si>
     <t>GitHub governance evidence capture plan</t>
   </si>
   <si>
@@ -353,10 +341,34 @@
     <t>Accepted after rework.</t>
   </si>
   <si>
-    <t>AI Usage Register entries for Member C</t>
-  </si>
-  <si>
-    <t>Drafted these register entries from the session record, stating the engineering task and the contribution for each, and left the Verification column for the student to complete on the ground that verification is the student's own act and cannot be supplied by the tool.</t>
+    <t>Verified that the scoring method aligned with taught methods during PMM381 and ensured that all drafted risk were real and accurate risks.</t>
+  </si>
+  <si>
+    <t>Verified that the 7 drafted concers made logical sense and verified that these concerns could become greater risks down the line.</t>
+  </si>
+  <si>
+    <t>Accepted and changed , The risks were aligned with real project risks but the method used for calculations was off , corrected it with knowledge gained from PMM 381</t>
+  </si>
+  <si>
+    <t>Accepted, The drafted concerns highlighted real concrens that we need to be aware of.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified and updated the column to show accurate content and ensured that the link was accurate. </t>
+  </si>
+  <si>
+    <t>Accepted. Guidance was appreciated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensured that the proposed solutions were standard and best practice. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted, used the drafted order list to strusture the current repo to comply with governance. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified that the proposed requirements were actually in the Master brief and ensured that they related to the tasks I was assigned to. </t>
+  </si>
+  <si>
+    <t>Accepted, Used the audit to ensure all needed outputs were created.</t>
   </si>
 </sst>
 </file>
@@ -366,7 +378,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,20 +404,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -562,13 +560,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -938,19 +936,19 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="B1:H40"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:H38"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="20.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="20.33203125" style="1" customWidth="1"/>
     <col min="5" max="6" width="37" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="40.28515625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="7" width="41.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="40.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
         <v>7</v>
       </c>
@@ -961,7 +959,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="2:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -984,7 +982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B3" s="5">
         <f t="shared" ref="B3:B8" si="0">DATE(2026,9,8)</f>
         <v>46273</v>
@@ -1008,7 +1006,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B4" s="7">
         <f t="shared" si="0"/>
         <v>46273</v>
@@ -1032,7 +1030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
         <f t="shared" si="0"/>
         <v>46273</v>
@@ -1056,7 +1054,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
         <f t="shared" si="0"/>
         <v>46273</v>
@@ -1080,7 +1078,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B7" s="7">
         <f t="shared" si="0"/>
         <v>46273</v>
@@ -1104,7 +1102,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <f t="shared" si="0"/>
         <v>46273</v>
@@ -1128,7 +1126,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B9" s="7">
         <f t="shared" ref="B9:B16" si="1">DATE(2026,9,9)</f>
         <v>46274</v>
@@ -1152,7 +1150,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B10" s="7">
         <f t="shared" si="1"/>
         <v>46274</v>
@@ -1176,7 +1174,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="72" x14ac:dyDescent="0.3">
       <c r="B11" s="7">
         <f t="shared" si="1"/>
         <v>46274</v>
@@ -1200,7 +1198,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B12" s="7">
         <f t="shared" si="1"/>
         <v>46274</v>
@@ -1224,7 +1222,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="7">
         <f t="shared" si="1"/>
         <v>46274</v>
@@ -1248,7 +1246,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B14" s="7">
         <f t="shared" si="1"/>
         <v>46274</v>
@@ -1272,7 +1270,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B15" s="7">
         <f t="shared" si="1"/>
         <v>46274</v>
@@ -1296,7 +1294,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B16" s="7">
         <f t="shared" si="1"/>
         <v>46274</v>
@@ -1320,7 +1318,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="102" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
         <v>66</v>
       </c>
@@ -1336,14 +1334,14 @@
       <c r="F17" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="138" x14ac:dyDescent="0.3">
       <c r="B18" s="11" t="s">
         <v>66</v>
       </c>
@@ -1354,21 +1352,21 @@
         <v>9</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="G18" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="B19" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>67</v>
@@ -1382,16 +1380,16 @@
       <c r="F19" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G19" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>67</v>
@@ -1400,21 +1398,21 @@
         <v>9</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="114.75" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="179.4" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>67</v>
@@ -1423,21 +1421,21 @@
         <v>9</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F21" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="138" x14ac:dyDescent="0.3">
+      <c r="B22" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="178.5" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>84</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>67</v>
@@ -1446,21 +1444,21 @@
         <v>9</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" ht="127.5" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>67</v>
@@ -1469,21 +1467,21 @@
         <v>9</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="B24" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>67</v>
@@ -1492,21 +1490,21 @@
         <v>9</v>
       </c>
       <c r="E24" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="G24" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="69" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>67</v>
@@ -1515,21 +1513,21 @@
         <v>9</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="63.75" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="B26" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>67</v>
@@ -1538,65 +1536,37 @@
         <v>9</v>
       </c>
       <c r="E26" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="H26" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G26" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="153" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -1605,7 +1575,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -1614,7 +1584,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -1623,7 +1593,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -1632,7 +1602,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -1641,7 +1611,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -1650,7 +1620,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="7"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -1659,7 +1629,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -1668,7 +1638,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -1677,7 +1647,7 @@
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="7"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -1686,29 +1656,11 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:H40">
+  <conditionalFormatting sqref="B3:H38">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
